--- a/excel-files/PASIG/RIZAL HIGH SCHOOL.xlsx
+++ b/excel-files/PASIG/RIZAL HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="228" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D19E3A0D-4735-40DB-BDD2-C1596AFD5F02}"/>
+  <xr:revisionPtr revIDLastSave="271" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03AD9BA8-C705-47EF-9810-559937199417}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="119">
   <si>
     <t>Grade Level</t>
   </si>
@@ -825,6 +825,7 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -836,9 +837,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3550,8 +3548,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <dimension ref="A1:I98"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.85546875" customWidth="1"/>
@@ -3561,7 +3559,7 @@
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="13" customFormat="1" ht="64.900000000000006" customHeight="1">
+    <row r="1" spans="1:9" s="13" customFormat="1" ht="64.900000000000006" customHeight="1">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -3586,8 +3584,9 @@
       <c r="H1" s="18" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="27.75" customHeight="1">
+      <c r="I1" s="40"/>
+    </row>
+    <row r="2" spans="1:9" ht="27.75" customHeight="1">
       <c r="A2" s="9">
         <v>7</v>
       </c>
@@ -3615,7 +3614,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="27.75" customHeight="1">
+    <row r="3" spans="1:9" ht="27.75" customHeight="1">
       <c r="A3" s="9">
         <v>7</v>
       </c>
@@ -3637,7 +3636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="27.75" customHeight="1">
+    <row r="4" spans="1:9" ht="27.75" customHeight="1">
       <c r="A4" s="9">
         <v>7</v>
       </c>
@@ -3651,7 +3650,7 @@
         <v>2429</v>
       </c>
       <c r="E4" s="9">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>9</v>
@@ -3665,7 +3664,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="27.75" customHeight="1">
+    <row r="5" spans="1:9" ht="27.75" customHeight="1">
       <c r="A5" s="9">
         <v>7</v>
       </c>
@@ -3675,19 +3674,26 @@
       <c r="C5" s="9">
         <v>1828</v>
       </c>
-      <c r="D5" s="9"/>
+      <c r="D5" s="9">
+        <v>2429</v>
+      </c>
       <c r="E5" s="9"/>
-      <c r="F5" s="11"/>
+      <c r="F5" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>1828</v>
+        <v>0</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="39" customHeight="1">
+        <v>601</v>
+      </c>
+      <c r="I5">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="39" customHeight="1">
       <c r="A6" s="9">
         <v>7</v>
       </c>
@@ -3715,7 +3721,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="27.75" customHeight="1">
+    <row r="7" spans="1:9" ht="27.75" customHeight="1">
       <c r="A7" s="9">
         <v>7</v>
       </c>
@@ -3729,7 +3735,7 @@
         <v>2429</v>
       </c>
       <c r="E7" s="9">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>9</v>
@@ -3743,7 +3749,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="27.75" customHeight="1">
+    <row r="8" spans="1:9" ht="27.75" customHeight="1">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -3771,7 +3777,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="27.75" customHeight="1">
+    <row r="9" spans="1:9" ht="27.75" customHeight="1">
       <c r="A9" s="9">
         <v>7</v>
       </c>
@@ -3781,19 +3787,26 @@
       <c r="C9" s="9">
         <v>1828</v>
       </c>
-      <c r="D9" s="9"/>
+      <c r="D9" s="9">
+        <v>2429</v>
+      </c>
       <c r="E9" s="9"/>
-      <c r="F9" s="11"/>
+      <c r="F9" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="G9" s="3">
         <f t="shared" si="0"/>
-        <v>1828</v>
+        <v>0</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="27.75" customHeight="1">
+        <v>601</v>
+      </c>
+      <c r="I9">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="27.75" customHeight="1">
       <c r="A10" s="9">
         <v>7</v>
       </c>
@@ -3821,7 +3834,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="27.75" customHeight="1">
+    <row r="11" spans="1:9" ht="27.75" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7"/>
@@ -3831,7 +3844,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" ht="27.75" customHeight="1">
+    <row r="12" spans="1:9" ht="27.75" customHeight="1">
       <c r="A12" s="9">
         <v>8</v>
       </c>
@@ -3853,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="27.75" customHeight="1">
+    <row r="13" spans="1:9" ht="27.75" customHeight="1">
       <c r="A13" s="9">
         <v>8</v>
       </c>
@@ -3875,7 +3888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="27.75" customHeight="1">
+    <row r="14" spans="1:9" ht="27.75" customHeight="1">
       <c r="A14" s="9">
         <v>8</v>
       </c>
@@ -3885,19 +3898,25 @@
       <c r="C14" s="9">
         <v>1999</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="11"/>
+      <c r="D14" s="9">
+        <v>1894</v>
+      </c>
+      <c r="E14" s="9">
+        <v>2025</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="G14" s="3">
         <f t="shared" si="2"/>
-        <v>1999</v>
+        <v>105</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="27.75" customHeight="1">
+    <row r="15" spans="1:9" ht="27.75" customHeight="1">
       <c r="A15" s="9">
         <v>8</v>
       </c>
@@ -3925,7 +3944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27.75" customHeight="1">
+    <row r="16" spans="1:9" ht="27.75" customHeight="1">
       <c r="A16" s="9">
         <v>8</v>
       </c>
@@ -3947,7 +3966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="27.75" customHeight="1">
+    <row r="17" spans="1:9" ht="27.75" customHeight="1">
       <c r="A17" s="9">
         <v>8</v>
       </c>
@@ -3957,19 +3976,26 @@
       <c r="C17" s="9">
         <v>1999</v>
       </c>
-      <c r="D17" s="9"/>
+      <c r="D17" s="9">
+        <v>1894</v>
+      </c>
       <c r="E17" s="9"/>
-      <c r="F17" s="11"/>
+      <c r="F17" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="G17" s="3">
         <f t="shared" si="2"/>
-        <v>1999</v>
+        <v>105</v>
       </c>
       <c r="H17" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="27.75" customHeight="1">
+      <c r="I17">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="27.75" customHeight="1">
       <c r="A18" s="9">
         <v>8</v>
       </c>
@@ -3991,7 +4017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="27.75" customHeight="1">
+    <row r="19" spans="1:9" ht="27.75" customHeight="1">
       <c r="A19" s="9">
         <v>8</v>
       </c>
@@ -4013,7 +4039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="27.75" customHeight="1">
+    <row r="20" spans="1:9" ht="27.75" customHeight="1">
       <c r="A20" s="9">
         <v>8</v>
       </c>
@@ -4035,7 +4061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="27.75" customHeight="1">
+    <row r="21" spans="1:9" ht="27.75" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7"/>
@@ -4045,7 +4071,7 @@
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:8" ht="27.75" customHeight="1">
+    <row r="22" spans="1:9" ht="27.75" customHeight="1">
       <c r="A22" s="9">
         <v>9</v>
       </c>
@@ -4067,7 +4093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="27.75" customHeight="1">
+    <row r="23" spans="1:9" ht="27.75" customHeight="1">
       <c r="A23" s="9">
         <v>9</v>
       </c>
@@ -4089,7 +4115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="27.75" customHeight="1">
+    <row r="24" spans="1:9" ht="27.75" customHeight="1">
       <c r="A24" s="9">
         <v>9</v>
       </c>
@@ -4111,7 +4137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="27.75" customHeight="1">
+    <row r="25" spans="1:9" ht="27.75" customHeight="1">
       <c r="A25" s="9">
         <v>9</v>
       </c>
@@ -4133,7 +4159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="27.75" customHeight="1">
+    <row r="26" spans="1:9" ht="27.75" customHeight="1">
       <c r="A26" s="9">
         <v>9</v>
       </c>
@@ -4155,7 +4181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="27.75" customHeight="1">
+    <row r="27" spans="1:9" ht="27.75" customHeight="1">
       <c r="A27" s="9">
         <v>9</v>
       </c>
@@ -4177,7 +4203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="27.75" customHeight="1">
+    <row r="28" spans="1:9" ht="27.75" customHeight="1">
       <c r="A28" s="9">
         <v>9</v>
       </c>
@@ -4199,7 +4225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" customHeight="1">
+    <row r="29" spans="1:9" ht="27.75" customHeight="1">
       <c r="A29" s="9">
         <v>9</v>
       </c>
@@ -4221,7 +4247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="27.75" customHeight="1">
+    <row r="30" spans="1:9" ht="27.75" customHeight="1">
       <c r="A30" s="9">
         <v>9</v>
       </c>
@@ -4243,7 +4269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:9" ht="27.75" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -4253,7 +4279,7 @@
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
     </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+    <row r="32" spans="1:9" ht="27.75" customHeight="1">
       <c r="A32" s="9">
         <v>10</v>
       </c>
@@ -5085,25 +5111,25 @@
       <c r="G77" s="3"/>
       <c r="H77" s="4"/>
     </row>
-    <row r="78" spans="1:8" ht="15"/>
-    <row r="79" spans="1:8" ht="15"/>
-    <row r="81" ht="15"/>
-    <row r="82" ht="15"/>
-    <row r="83" ht="15"/>
-    <row r="85" ht="15"/>
-    <row r="86" ht="15"/>
-    <row r="87" ht="15"/>
-    <row r="88" ht="15"/>
-    <row r="89" ht="15"/>
-    <row r="90" ht="15"/>
-    <row r="91" ht="15"/>
-    <row r="92" ht="15"/>
-    <row r="93" ht="15"/>
-    <row r="94" ht="15"/>
-    <row r="95" ht="15"/>
-    <row r="96" ht="15"/>
-    <row r="97" ht="15"/>
-    <row r="98" ht="15"/>
+    <row r="78" spans="1:8"/>
+    <row r="79" spans="1:8"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="D50:E50 D46:E46 D45 D47 D54:E56 C50:C56 D42:E44 C1:E41" name="Textbooks"/>
@@ -5111,11 +5137,11 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12:E20 E22:E30 E32:E40 E2:E10 E46 E50 E54:E56 E42:E44" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F10 F22:F30 F32:F40 F12:F20 F42:F56" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42:E56 E32:E40 E22:E30 E12:E20 E2:E10" xr:uid="{C90DBFCB-DD6F-47CB-918D-2133687D17A5}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5127,7 +5153,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5157,38 +5183,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="27" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="44"/>
+      <c r="X1" s="44"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="44"/>
+      <c r="AA1" s="44"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="14" t="s">
@@ -13113,186 +13139,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13312,8 +13158,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13361,38 +13207,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="27" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="34"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="44"/>
+      <c r="X1" s="44"/>
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="44"/>
+      <c r="AA1" s="44"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="14" t="s">
@@ -16689,11 +16535,11 @@
       <c r="E52" s="33"/>
       <c r="F52" s="31"/>
       <c r="G52" s="33"/>
-      <c r="H52" s="44">
+      <c r="H52" s="33">
         <f>IF((D52-E52)&lt;0,0,(D52-E52))</f>
         <v>0</v>
       </c>
-      <c r="I52" s="44">
+      <c r="I52" s="33">
         <f>IF((E52-D52)&lt;0,0,(E52-D52))</f>
         <v>0</v>
       </c>
@@ -16752,11 +16598,11 @@
       <c r="E53" s="33"/>
       <c r="F53" s="31"/>
       <c r="G53" s="33"/>
-      <c r="H53" s="44">
+      <c r="H53" s="33">
         <f>IF((D53-E53)&lt;0,0,(D53-E53))</f>
         <v>0</v>
       </c>
-      <c r="I53" s="44">
+      <c r="I53" s="33">
         <f>IF((E53-D53)&lt;0,0,(E53-D53))</f>
         <v>0</v>
       </c>
@@ -16815,11 +16661,11 @@
       <c r="E54" s="33"/>
       <c r="F54" s="31"/>
       <c r="G54" s="33"/>
-      <c r="H54" s="44">
+      <c r="H54" s="33">
         <f>IF((D54-E54)&lt;0,0,(D54-E54))</f>
         <v>0</v>
       </c>
-      <c r="I54" s="44">
+      <c r="I54" s="33">
         <f>IF((E54-D54)&lt;0,0,(E54-D54))</f>
         <v>0</v>
       </c>
@@ -16878,11 +16724,11 @@
       <c r="E55" s="33"/>
       <c r="F55" s="31"/>
       <c r="G55" s="33"/>
-      <c r="H55" s="44">
+      <c r="H55" s="33">
         <f>IF((D55-E55)&lt;0,0,(D55-E55))</f>
         <v>0</v>
       </c>
-      <c r="I55" s="44">
+      <c r="I55" s="33">
         <f>IF((E55-D55)&lt;0,0,(E55-D55))</f>
         <v>0</v>
       </c>
@@ -16941,11 +16787,11 @@
       <c r="E56" s="33"/>
       <c r="F56" s="31"/>
       <c r="G56" s="33"/>
-      <c r="H56" s="44">
+      <c r="H56" s="33">
         <f>IF((D56-E56)&lt;0,0,(D56-E56))</f>
         <v>0</v>
       </c>
-      <c r="I56" s="44">
+      <c r="I56" s="33">
         <f>IF((E56-D56)&lt;0,0,(E56-D56))</f>
         <v>0</v>
       </c>
@@ -17004,11 +16850,11 @@
       <c r="E57" s="33"/>
       <c r="F57" s="31"/>
       <c r="G57" s="33"/>
-      <c r="H57" s="44">
+      <c r="H57" s="33">
         <f>IF((D57-E57)&lt;0,0,(D57-E57))</f>
         <v>0</v>
       </c>
-      <c r="I57" s="44">
+      <c r="I57" s="33">
         <f>IF((E57-D57)&lt;0,0,(E57-D57))</f>
         <v>0</v>
       </c>
@@ -17067,11 +16913,11 @@
       <c r="E58" s="33"/>
       <c r="F58" s="31"/>
       <c r="G58" s="33"/>
-      <c r="H58" s="44">
+      <c r="H58" s="33">
         <f>IF((D58-E58)&lt;0,0,(D58-E58))</f>
         <v>0</v>
       </c>
-      <c r="I58" s="44">
+      <c r="I58" s="33">
         <f>IF((E58-D58)&lt;0,0,(E58-D58))</f>
         <v>0</v>
       </c>
@@ -17130,11 +16976,11 @@
       <c r="E59" s="33"/>
       <c r="F59" s="31"/>
       <c r="G59" s="33"/>
-      <c r="H59" s="44">
+      <c r="H59" s="33">
         <f>IF((D59-E59)&lt;0,0,(D59-E59))</f>
         <v>0</v>
       </c>
-      <c r="I59" s="44">
+      <c r="I59" s="33">
         <f>IF((E59-D59)&lt;0,0,(E59-D59))</f>
         <v>0</v>
       </c>
@@ -17193,11 +17039,11 @@
       <c r="E60" s="33"/>
       <c r="F60" s="31"/>
       <c r="G60" s="33"/>
-      <c r="H60" s="44">
+      <c r="H60" s="33">
         <f>IF((D60-E60)&lt;0,0,(D60-E60))</f>
         <v>0</v>
       </c>
-      <c r="I60" s="44">
+      <c r="I60" s="33">
         <f>IF((E60-D60)&lt;0,0,(E60-D60))</f>
         <v>0</v>
       </c>
@@ -17256,11 +17102,11 @@
       <c r="E61" s="33"/>
       <c r="F61" s="31"/>
       <c r="G61" s="33"/>
-      <c r="H61" s="44">
+      <c r="H61" s="33">
         <f>IF((D61-E61)&lt;0,0,(D61-E61))</f>
         <v>0</v>
       </c>
-      <c r="I61" s="44">
+      <c r="I61" s="33">
         <f>IF((E61-D61)&lt;0,0,(E61-D61))</f>
         <v>0</v>
       </c>
@@ -17319,11 +17165,11 @@
       <c r="E62" s="33"/>
       <c r="F62" s="31"/>
       <c r="G62" s="33"/>
-      <c r="H62" s="44">
+      <c r="H62" s="33">
         <f>IF((D62-E62)&lt;0,0,(D62-E62))</f>
         <v>0</v>
       </c>
-      <c r="I62" s="44">
+      <c r="I62" s="33">
         <f>IF((E62-D62)&lt;0,0,(E62-D62))</f>
         <v>0</v>
       </c>
@@ -17382,11 +17228,11 @@
       <c r="E63" s="33"/>
       <c r="F63" s="31"/>
       <c r="G63" s="33"/>
-      <c r="H63" s="44">
+      <c r="H63" s="33">
         <f>IF((D63-E63)&lt;0,0,(D63-E63))</f>
         <v>0</v>
       </c>
-      <c r="I63" s="44">
+      <c r="I63" s="33">
         <f>IF((E63-D63)&lt;0,0,(E63-D63))</f>
         <v>0</v>
       </c>
@@ -17445,11 +17291,11 @@
       <c r="E64" s="33"/>
       <c r="F64" s="31"/>
       <c r="G64" s="33"/>
-      <c r="H64" s="44">
+      <c r="H64" s="33">
         <f>IF((D64-E64)&lt;0,0,(D64-E64))</f>
         <v>0</v>
       </c>
-      <c r="I64" s="44">
+      <c r="I64" s="33">
         <f>IF((E64-D64)&lt;0,0,(E64-D64))</f>
         <v>0</v>
       </c>
@@ -17508,11 +17354,11 @@
       <c r="E65" s="33"/>
       <c r="F65" s="31"/>
       <c r="G65" s="33"/>
-      <c r="H65" s="44">
+      <c r="H65" s="33">
         <f>IF((D65-E65)&lt;0,0,(D65-E65))</f>
         <v>0</v>
       </c>
-      <c r="I65" s="44">
+      <c r="I65" s="33">
         <f>IF((E65-D65)&lt;0,0,(E65-D65))</f>
         <v>0</v>
       </c>
@@ -18328,197 +18174,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="15">
-      <c r="J88" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="89" spans="1:27" ht="15">
-      <c r="J89" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="90" spans="1:27" ht="15">
-      <c r="J90" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="91" spans="1:27" ht="15">
-      <c r="J91" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="92" spans="1:27" ht="15">
-      <c r="J92" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="93" spans="1:27" ht="15">
-      <c r="J93" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="94" spans="1:27" ht="15">
-      <c r="J94" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="95" spans="1:27" ht="15">
-      <c r="J95" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27" ht="15">
-      <c r="J96" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="97" spans="10:10" ht="15">
-      <c r="J97" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="98" spans="10:10" ht="15">
-      <c r="J98" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="99" spans="10:10" ht="15">
-      <c r="J99" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="100" spans="10:10" ht="15">
-      <c r="J100" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="101" spans="10:10" ht="15">
-      <c r="J101" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="102" spans="10:10" ht="15">
-      <c r="J102" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="103" spans="10:10" ht="15">
-      <c r="J103" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="104" spans="10:10" ht="15">
-      <c r="J104" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="105" spans="10:10" ht="15">
-      <c r="J105" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="106" spans="10:10" ht="15">
-      <c r="J106" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="107" spans="10:10" ht="15">
-      <c r="J107" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="108" spans="10:10" ht="15">
-      <c r="J108" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="109" spans="10:10" ht="15">
-      <c r="J109" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="110" spans="10:10" ht="15">
-      <c r="J110" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="111" spans="10:10" ht="15">
-      <c r="J111" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="112" spans="10:10" ht="15">
-      <c r="J112" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="113" spans="10:10" ht="15">
-      <c r="J113" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="114" spans="10:10" ht="15">
-      <c r="J114" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="115" spans="10:10" ht="15">
-      <c r="J115" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="116" spans="10:10" ht="15">
-      <c r="J116" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="117" spans="10:10" ht="15">
-      <c r="J117" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="118" spans="10:10" ht="15"/>
-    <row r="119" spans="10:10" ht="15"/>
-    <row r="120" spans="10:10" ht="15"/>
-    <row r="121" spans="10:10" ht="15"/>
-    <row r="122" spans="10:10" ht="15"/>
-    <row r="123" spans="10:10" ht="15"/>
-    <row r="124" spans="10:10" ht="15"/>
-    <row r="125" spans="10:10" ht="15"/>
-    <row r="126" spans="10:10" ht="15"/>
-    <row r="127" spans="10:10" ht="15"/>
-    <row r="128" spans="10:10" ht="15"/>
+    <row r="88" spans="1:27" ht="15"/>
+    <row r="89" spans="1:27" ht="15"/>
+    <row r="90" spans="1:27" ht="15"/>
+    <row r="91" spans="1:27" ht="15"/>
+    <row r="92" spans="1:27" ht="15"/>
+    <row r="93" spans="1:27" ht="15"/>
+    <row r="94" spans="1:27" ht="15"/>
+    <row r="95" spans="1:27" ht="15"/>
+    <row r="96" spans="1:27" ht="15"/>
+    <row r="97" ht="15"/>
+    <row r="98" ht="15"/>
+    <row r="99" ht="15"/>
+    <row r="100" ht="15"/>
+    <row r="101" ht="15"/>
+    <row r="102" ht="15"/>
+    <row r="103" ht="15"/>
+    <row r="104" ht="15"/>
+    <row r="105" ht="15"/>
+    <row r="106" ht="15"/>
+    <row r="107" ht="15"/>
+    <row r="108" ht="15"/>
+    <row r="109" ht="15"/>
+    <row r="110" ht="15"/>
+    <row r="111" ht="15"/>
+    <row r="112" ht="15"/>
+    <row r="113" ht="15"/>
+    <row r="114" ht="15"/>
+    <row r="115" ht="15"/>
+    <row r="116" ht="15"/>
+    <row r="117" ht="15"/>
+    <row r="118" ht="15"/>
+    <row r="119" ht="15"/>
+    <row r="120" ht="15"/>
+    <row r="121" ht="15"/>
+    <row r="122" ht="15"/>
+    <row r="123" ht="15"/>
+    <row r="124" ht="15"/>
+    <row r="125" ht="15"/>
+    <row r="126" ht="15"/>
+    <row r="127" ht="15"/>
+    <row r="128" ht="15"/>
     <row r="129" ht="15"/>
     <row r="130" ht="15"/>
     <row r="131" ht="15"/>
@@ -18546,8 +18242,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S51:S65 Y51:Y65 G51:G65 M3:M13 G3:G13 Y3:Y13 S3:S13 S15:S25 M15:M25 G15:G25 Y15:Y25 Y27:Y37 S27:S37 M27:M37 G27:G37 G39:G49 Y39:Y49 S39:S49 M39:M49 M51:M65" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3:X13 X15:X25 X27:X37 X39:X49 L3:L13 L15:L25 L27:L37 L39:L49 R3:R13 R15:R25 R27:R37 R39:R49 F3:F13 F15:F25 F27:F37 X51:X65 F51:F65 R51:R65 L51:L65 F39:F49" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F67:F87 F51:F65 F39:F49 F27:F37 F15:F25 F3:F13 L67:L87 L51:L65 L39:L49 L27:L37 L15:L25 L3:L13 R67:R87 R51:R65 R39:R49 R27:R37 R15:R25 R3:R13 X67:X87 X51:X65 X39:X49 X27:X37 X15:X25 X3:X13" xr:uid="{D1307BC6-63B2-4E23-9966-8C4983515AE2}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
